--- a/data/raw/LM_2014_2022_1.ACEPTACION.xlsx
+++ b/data/raw/LM_2014_2022_1.ACEPTACION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\off_line_files\licencias_dsp\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AE0EF7-22B6-4E20-A801-D6466C44549B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB08A36-41C4-405A-9C3F-3B29894C2637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16485" windowWidth="29040" windowHeight="15720" xr2:uid="{F4C8F593-6C9C-4587-B07C-92B2D6D860AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F4C8F593-6C9C-4587-B07C-92B2D6D860AF}"/>
   </bookViews>
   <sheets>
     <sheet name="aceptadas" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1061,6 +1061,7 @@
           <cell r="N38">
             <v>3440</v>
           </cell>
+          <cell r="O38"/>
           <cell r="S38">
             <v>124</v>
           </cell>
@@ -1088,6 +1089,7 @@
           <cell r="AA38">
             <v>2</v>
           </cell>
+          <cell r="AB38"/>
           <cell r="AC38">
             <v>211</v>
           </cell>
@@ -1097,6 +1099,7 @@
           <cell r="AE38">
             <v>65</v>
           </cell>
+          <cell r="AF38"/>
         </row>
         <row r="39">
           <cell r="B39">
@@ -1604,6 +1607,7 @@
           <cell r="AC44">
             <v>3903</v>
           </cell>
+          <cell r="AD44"/>
           <cell r="AE44">
             <v>5312</v>
           </cell>
@@ -1612,9 +1616,25 @@
           </cell>
         </row>
         <row r="45">
+          <cell r="B45"/>
+          <cell r="C45"/>
+          <cell r="D45"/>
+          <cell r="E45"/>
+          <cell r="F45"/>
+          <cell r="G45"/>
+          <cell r="H45"/>
+          <cell r="I45"/>
+          <cell r="J45"/>
+          <cell r="K45"/>
+          <cell r="L45"/>
+          <cell r="M45"/>
+          <cell r="N45"/>
+          <cell r="O45"/>
           <cell r="S45">
             <v>1</v>
           </cell>
+          <cell r="T45"/>
+          <cell r="U45"/>
           <cell r="V45">
             <v>1</v>
           </cell>
@@ -1624,6 +1644,14 @@
           <cell r="X45">
             <v>1</v>
           </cell>
+          <cell r="Y45"/>
+          <cell r="Z45"/>
+          <cell r="AA45"/>
+          <cell r="AB45"/>
+          <cell r="AC45"/>
+          <cell r="AD45"/>
+          <cell r="AE45"/>
+          <cell r="AF45"/>
         </row>
         <row r="52">
           <cell r="B52">
@@ -1665,6 +1693,7 @@
           <cell r="N52">
             <v>3310</v>
           </cell>
+          <cell r="O52"/>
           <cell r="S52">
             <v>1639</v>
           </cell>
@@ -1790,6 +1819,7 @@
           <cell r="AE53">
             <v>3430</v>
           </cell>
+          <cell r="AF53"/>
         </row>
         <row r="54">
           <cell r="B54">
@@ -1959,6 +1989,7 @@
           <cell r="AE55">
             <v>2591</v>
           </cell>
+          <cell r="AF55"/>
         </row>
         <row r="56">
           <cell r="B56">
@@ -2128,6 +2159,7 @@
           <cell r="AE57">
             <v>9945</v>
           </cell>
+          <cell r="AF57"/>
         </row>
         <row r="58">
           <cell r="B58">
@@ -2297,6 +2329,7 @@
           <cell r="AE59">
             <v>6062</v>
           </cell>
+          <cell r="AF59"/>
         </row>
         <row r="60">
           <cell r="B60">
@@ -2380,6 +2413,7 @@
           <cell r="AE60">
             <v>6137</v>
           </cell>
+          <cell r="AF60"/>
         </row>
         <row r="61">
           <cell r="B61">
@@ -2463,6 +2497,7 @@
           <cell r="AE61">
             <v>2622</v>
           </cell>
+          <cell r="AF61"/>
         </row>
         <row r="62">
           <cell r="B62">
@@ -2718,6 +2753,7 @@
           <cell r="AE64">
             <v>1804</v>
           </cell>
+          <cell r="AF64"/>
         </row>
         <row r="65">
           <cell r="B65">
@@ -2973,8 +3009,23 @@
           <cell r="AE67">
             <v>2063</v>
           </cell>
+          <cell r="AF67"/>
         </row>
         <row r="68">
+          <cell r="B68"/>
+          <cell r="C68"/>
+          <cell r="D68"/>
+          <cell r="E68"/>
+          <cell r="F68"/>
+          <cell r="G68"/>
+          <cell r="H68"/>
+          <cell r="I68"/>
+          <cell r="J68"/>
+          <cell r="K68"/>
+          <cell r="L68"/>
+          <cell r="M68"/>
+          <cell r="N68"/>
+          <cell r="O68"/>
           <cell r="S68">
             <v>1669</v>
           </cell>
@@ -3014,6 +3065,7 @@
           <cell r="AE68">
             <v>562</v>
           </cell>
+          <cell r="AF68"/>
         </row>
       </sheetData>
       <sheetData sheetId="8">
@@ -3164,6 +3216,7 @@
           <cell r="A20" t="str">
             <v>Sin información</v>
           </cell>
+          <cell r="B20"/>
           <cell r="C20">
             <v>35</v>
           </cell>
@@ -3294,6 +3347,7 @@
           <cell r="N28">
             <v>235153</v>
           </cell>
+          <cell r="O28"/>
           <cell r="S28">
             <v>188195</v>
           </cell>
@@ -3377,6 +3431,7 @@
           <cell r="N29">
             <v>278862</v>
           </cell>
+          <cell r="O29"/>
           <cell r="S29">
             <v>238589</v>
           </cell>
@@ -3421,21 +3476,40 @@
           </cell>
         </row>
         <row r="30">
+          <cell r="B30"/>
+          <cell r="C30"/>
+          <cell r="D30"/>
+          <cell r="E30"/>
+          <cell r="F30"/>
+          <cell r="G30"/>
+          <cell r="H30"/>
+          <cell r="I30"/>
+          <cell r="J30"/>
+          <cell r="K30"/>
+          <cell r="L30"/>
+          <cell r="M30"/>
+          <cell r="N30"/>
+          <cell r="O30"/>
           <cell r="S30">
             <v>6</v>
           </cell>
           <cell r="T30">
             <v>1</v>
           </cell>
+          <cell r="U30"/>
           <cell r="V30">
             <v>9</v>
           </cell>
+          <cell r="W30"/>
           <cell r="X30">
             <v>1</v>
           </cell>
           <cell r="Y30">
             <v>7</v>
           </cell>
+          <cell r="Z30"/>
+          <cell r="AA30"/>
+          <cell r="AB30"/>
           <cell r="AC30">
             <v>2</v>
           </cell>
@@ -3445,6 +3519,7 @@
           <cell r="AE30">
             <v>3</v>
           </cell>
+          <cell r="AF30"/>
         </row>
         <row r="31">
           <cell r="B31">
